--- a/Data_Fig_03_R,S,T.xlsx
+++ b/Data_Fig_03_R,S,T.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Speed_m_s</t>
+          <t>Speed_BL_s</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -434,7 +434,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Acceleration_m_s2</t>
+          <t>Acceleration_BL_s2</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
